--- a/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est assise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable. Papa dit : on mange ensemble. On mange à table. Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
+          <t>C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est assise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable. On mange ensemble. On mange à table. Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est assise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable.
+papa|On mange ensemble. On mange à table.
+narrateur|Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Céleste va manger. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Céleste est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Céleste boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Céleste va manger. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Céleste est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Céleste boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Céleste s'assoit au petit-déjeuner</t>
+          <t>Le rond jaune du couloir</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La lampe du couloir fait un rond jaune. Un oiseau tape le volet. Ça sent le lait chaud. Victorina amène sa chaise. On mange assis.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est assise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable. On mange ensemble. On mange à table. Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
+          <t>La petite lampe du couloir est encore allumée. Elle fait un rond jaune. Les rideaux de la cuisine sont fermés. Le village dort encore un peu. Un oiseau tape le volet. Toc. Toc. Ça sent le lait chaud. Ça sent aussi le pain. Papa marche en pantoufles. Les pantoufles font chut, chut. Victorina vit ici, avec papa et maman. Elle sort de sa chambre. Sa couverture est encore chaude. J'ai entendu l'oiseau ! Moi aussi. Il dit bonjour. Victorina, le lait est prêt. Viens t'asseoir. Victorina va vers la table. Le carrelage est un peu froid. Elle voit les bols. Les bols sont blancs, tout ronds. Elle voit sa chaise. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Victorina. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. Le bois est lisse. Un peu de lait a fait un rond. Tu as vu la petite vapeur ? Elle danse. Le lait est tiède. Le pain est croustillant. On attend un petit moment. Victorina tient sa cuillère. Elle reste assise.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1329,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est assise. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable.
-papa|On mange ensemble. On mange à table.
-narrateur|Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La petite lampe du couloir est encore allumée.
+narrateur|Elle fait un rond jaune.
+narrateur|Les rideaux de la cuisine sont fermés.
+narrateur|Le village dort encore un peu.
+narrateur|Un oiseau tape le volet.
+narrateur|Toc. Toc.
+narrateur|Ça sent le lait chaud.
+narrateur|Ça sent aussi le pain.
+narrateur|Papa marche en pantoufles.
+narrateur|Les pantoufles font chut, chut.
+narrateur|Victorina vit ici, avec papa et maman.
+narrateur|Elle sort de sa chambre.
+narrateur|Sa couverture est encore chaude.
+enfant-f|J'ai entendu l'oiseau !
+papa|Moi aussi.
+papa|Il dit bonjour.
+maman|Victorina, le lait est prêt.
+maman|Viens t'asseoir.
+narrateur|Victorina va vers la table.
+narrateur|Le carrelage est un peu froid.
+narrateur|Elle voit les bols.
+narrateur|Les bols sont blancs, tout ronds.
+narrateur|Elle voit sa chaise.
+narrateur|Elle tire un peu la chaise.
+narrateur|Elle s'assoit.
+narrateur|Elle pose les pieds par terre.
+maman|Bravo, Victorina.
+maman|Tu es bien assise.
+narrateur|Papa s'assoit aussi.
+narrateur|Maman s'assoit près d'elle.
+papa|On est ensemble.
+papa|On mange à table.
+narrateur|Sa chaise ne bouge plus.
+maman|Tu poses les mains sur la table ?
+narrateur|Elle pose les mains.
+narrateur|Le bois est lisse.
+narrateur|Un peu de lait a fait un rond.
+papa|Tu as vu la petite vapeur ?
+enfant-f|Elle danse.
+narrateur|Le lait est tiède.
+narrateur|Le pain est croustillant.
+maman|On attend un petit moment.
+narrateur|Victorina tient sa cuillère.
+narrateur|Elle reste assise.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>volet,chaise</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Céleste va manger. Que fait-elle ?</t>
+          <t>Victorina va manger. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Céleste va manger. Que fait-elle ?</t>
+          <t>narrateur|Victorina va manger.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Céleste est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>Victorina est assise. Elle est à table. On est tous assis. On est ensemble. Le bol attend. Ta chaise reste à table ? Oui. Victorina reste assise. L'oiseau tape encore, tout loin. Tu restes avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1733,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Céleste est assise. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>narrateur|Victorina est assise.
+narrateur|Elle est à table.
+papa|On est tous assis.
+maman|On est ensemble.
+narrateur|Le bol attend.
+papa|Ta chaise reste à table ?
+enfant-f|Oui.
+narrateur|Victorina reste assise.
+narrateur|L'oiseau tape encore, tout loin.
+maman|Tu restes avec nous ?
+enfant-f|Oui.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Céleste boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit papa.</t>
+          <t>Maman coupe une pomme. La pomme sent le sucré. Tu prends ta cuillère ? Victorina prend sa cuillère. Tu restes assise. Elle goûte le lait. C'est tiède. C'est bon. Bravo, Victorina. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Victorina. Ils mangent ensemble. Victorina reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Victorina. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1912,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Céleste boit une gorgée. Elle reste assise jusqu'à la fin. Merci, dit papa.</t>
+          <t>narrateur|Maman coupe une pomme.
+narrateur|La pomme sent le sucré.
+maman|Tu prends ta cuillère ?
+narrateur|Victorina prend sa cuillère.
+papa|Tu restes assise.
+narrateur|Elle goûte le lait.
+enfant-f|C'est tiède.
+enfant-f|C'est bon.
+maman|Bravo, Victorina.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+papa|Bon appétit.
+maman|Bon appétit, Victorina.
+narrateur|Ils mangent ensemble.
+narrateur|Victorina reste assise.
+papa|Encore une petite cuillère ?
+narrateur|Encore une cuillère.
+papa|Tu restes assise. Bravo.
+enfant-f|Merci, maman.
+enfant-f|Merci, papa.
+maman|Merci, Victorina.
+narrateur|Elle boit une gorgée.
+narrateur|Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1962,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'oiseau s'en va. Le rond jaune s'éteint. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2102,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'oiseau s'en va.
+narrateur|Le rond jaune s'éteint.
+papa|On a mangé assis, ensemble.
+enfant-f|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;C'est le matin. Céleste sent le pain chaud. Maman pose les bols. Papa met le lait. Céleste a faim. Elle va à table. Elle pose les fesses sur la chaise. Elle est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Elle est assise à table. Papa s'assoit aussi. Maman s'assoit près d'elle. Ils mangent ensemble. Céleste tient sa cuillère. Elle mange assise. La chaise est stable. Papa dit : on mange ensemble. On mange à table. Céleste sourit. Elle reste assise. Maman coupe la pomme. Céleste attend, assise. Ils sont ensemble à table. Le lait est tiède. Le pain est croustillant.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La petite lampe du couloir est encore allumée. Elle fait un rond jaune. Les rideaux de la cuisine sont fermés. Le village dort encore un peu. Un oiseau tape le volet. Toc. Toc. Ça sent le lait chaud. Ça sent aussi le pain. Papa marche en pantoufles. Les pantoufles font chut, chut. Victorina vit ici, avec papa et maman. Elle sort de sa chambre. Sa couverture est encore chaude. J'ai entendu l'oiseau ! Moi aussi. Il dit bonjour. Victorina, le lait est prêt. Viens t'asseoir. Victorina va vers la table. Le carrelage est un peu froid. Elle voit les bols. Les bols sont blancs, tout ronds. Elle voit sa chaise. Elle tire un peu la chaise. Elle s'assoit. Elle pose les pieds par terre. Bravo, Victorina. Tu es bien assise. Papa s'assoit aussi. Maman s'assoit près d'elle. On est ensemble. On mange à table. Sa chaise ne bouge plus. Tu poses les mains sur la table ? Elle pose les mains. Le bois est lisse. Un peu de lait a fait un rond. Tu as vu la petite vapeur ? Elle danse. Le lait est tiède. Le pain est croustillant. On attend un petit moment. Victorina tient sa cuillère. Elle reste assise.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Céleste va manger. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina va manger. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1564,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Céleste est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina est assise. Elle est à table. On est tous assis. On est ensemble. Le bol attend. Ta chaise reste à table ? Oui. Victorina reste assise. L'oiseau tape encore, tout loin. Tu restes avec nous ? Oui. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1747,7 +1746,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1772,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman coupe une pomme. La pomme sent le sucré. Tu prends ta cuillère ? Victorina prend sa cuillère. Tu restes assise. Elle goûte le lait. C'est tiède. C'est bon. Bravo, Victorina. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Victorina. Ils mangent ensemble. Victorina reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Victorina. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
+          <t>Maman coupe une pomme. La pomme sent le sucré. Tu prends ta cuillère ? Victorina prend sa cuillère. Tu restes assise. Elle goûte le lait. C'est tiède. C'est bon. Bravo, Victorina. Tu as goûté. Bon appétit. Bon appétit, Victorina. Ils mangent ensemble. Victorina reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Victorina. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Céleste boit une gorgée. Elle reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e jusqu'à la fin. Merci, dit papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman coupe une pomme. La pomme sent le sucré. Tu prends ta cuillère ? Victorina prend sa cuillère. Tu restes assise. Elle goûte le lait. C'est tiède. C'est bon. Bravo, Victorina. Tu as goûté. Bon appétit. Bon appétit, Victorina. Ils mangent ensemble. Victorina reste assise. Encore une petite cuillère ? Encore une cuillère. Tu restes assise. Bravo. Merci, maman. Merci, papa. Merci, Victorina. Elle boit une gorgée. Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1920,6 @@
 enfant-f|C'est bon.
 maman|Bravo, Victorina.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 papa|Bon appétit.
 maman|Bon appétit, Victorina.
 narrateur|Ils mangent ensemble.
@@ -1937,7 +1934,6 @@
 narrateur|Elle reste assise jusqu'à la fin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1962,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'oiseau s'en va. Le rond jaune s'éteint. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>L'oiseau s'en va. Le rond jaune s'éteint. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'oiseau s'en va. Le rond jaune s'éteint. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,12 +2102,9 @@
 narrateur|Le rond jaune s'éteint.
 papa|On a mangé assis, ensemble.
 enfant-f|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-03.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Céleste, papa, maman</t>
+          <t>Victorina, papa, maman</t>
         </is>
       </c>
     </row>
